--- a/public/Guia/7000-Recaudado-CuentasConceptos.xlsx
+++ b/public/Guia/7000-Recaudado-CuentasConceptos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A85BE93-948F-4CA5-8558-8DA4BDECB435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A80DCC5-FB95-440E-8A40-C6171C96BFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
   <si>
     <t>cuenta</t>
   </si>
@@ -57,15 +57,6 @@
   </si>
   <si>
     <t>Contable - Abono</t>
-  </si>
-  <si>
-    <t>5.2.5.9.01.04</t>
-  </si>
-  <si>
-    <t>III.1.4 TRANSFERENCIAS, ASIGNACIONES, SUBSIDIOS Y OTRAS AYUDAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por el devengado por prestaciones de pensiones y jubilaciones </t>
   </si>
   <si>
     <t>Contable - Cargo</t>
@@ -513,97 +504,97 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -611,13 +602,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
@@ -625,13 +616,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="s">
-        <v>22</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
@@ -639,13 +630,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -956,15 +947,9 @@
       <c r="C72" s="2"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>

--- a/public/Guia/7000-Recaudado-CuentasConceptos.xlsx
+++ b/public/Guia/7000-Recaudado-CuentasConceptos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A80DCC5-FB95-440E-8A40-C6171C96BFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103315A0-3CC6-4754-A767-89B88FACABFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
   <si>
     <t>cuenta</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>VII. INVERSIONES FINANCIERAS Y OTRAS PROVISIONES E INGRESOS POR VENTA DE BIENES Y PRESTACION DE SERVICIOS</t>
+  </si>
+  <si>
+    <t>1.1.1.1.01.01</t>
   </si>
 </sst>
 </file>
@@ -643,9 +646,18 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>

--- a/public/Guia/7000-Recaudado-CuentasConceptos.xlsx
+++ b/public/Guia/7000-Recaudado-CuentasConceptos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dmijangos\Documents\SAC-IPE\public\Guia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103315A0-3CC6-4754-A767-89B88FACABFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F183A37-87A8-48F4-AA5A-D939315CEE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BA794CD9-A794-4D6D-97A5-04484BD59B08}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="23">
   <si>
     <t>cuenta</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t>1.1.1.1.01.01</t>
+  </si>
+  <si>
+    <t>8.1.2.4.1.7.1.02.01</t>
+  </si>
+  <si>
+    <t>2.1.9.1.01.01</t>
   </si>
 </sst>
 </file>
@@ -507,7 +513,7 @@
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
@@ -516,12 +522,12 @@
         <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -530,12 +536,12 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -544,12 +550,12 @@
         <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -558,12 +564,12 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -572,12 +578,12 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
@@ -591,7 +597,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
@@ -600,12 +606,12 @@
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -614,12 +620,12 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
@@ -628,12 +634,12 @@
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
@@ -642,118 +648,272 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
